--- a/Result/profitability/8155.xlsx
+++ b/Result/profitability/8155.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>1.745</v>
+        <v>2.08</v>
       </c>
       <c r="N2" t="n">
-        <v>16.98375</v>
+        <v>18.35625</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.66</v>
       </c>
       <c r="M3" t="n">
-        <v>1.74125</v>
+        <v>1.98125</v>
       </c>
       <c r="N3" t="n">
-        <v>16.84625</v>
+        <v>17.845</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -8558,6 +8558,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>8155</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1594</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1215</v>
+      </c>
+      <c r="E65" t="n">
+        <v>380</v>
+      </c>
+      <c r="F65" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="G65" t="n">
+        <v>235</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>14.72%</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>8</v>
+      </c>
+      <c r="J65" t="n">
+        <v>242</v>
+      </c>
+      <c r="K65" t="n">
+        <v>207</v>
+      </c>
+      <c r="L65" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.96625</v>
+      </c>
+      <c r="N65" t="n">
+        <v>18.005</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0.0243161094224924</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>-0.240000000000002</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-0.009979209979210091</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>-18.73684210526316</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>2.339410939691445</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
